--- a/practice-files/day03-筛选与排序.xlsx
+++ b/practice-files/day03-筛选与排序.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单明细" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -579,19 +578,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -655,26 +641,26 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>iPhone 15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>550.1799999999999</v>
+        <v>2231.4</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1650.54</v>
+        <v>4462.8</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -691,7 +677,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>滑雪手套</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -700,22 +686,22 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2104.8</v>
+        <v>1782.76</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>8419.200000000001</v>
+        <v>1782.76</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
     </row>
@@ -727,31 +713,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>围巾羊绒</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1330.47</v>
+        <v>1817</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2660.94</v>
+        <v>9085</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -763,31 +749,31 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1138.41</v>
+        <v>1779.12</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1138.41</v>
+        <v>1779.12</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -799,31 +785,31 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>巧克力礼盒</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>871.92</v>
+        <v>490.77</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3487.68</v>
+        <v>1472.31</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -835,31 +821,31 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2875.37</v>
+        <v>2546.06</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>14376.85</v>
+        <v>12730.3</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>北京</t>
         </is>
       </c>
     </row>
@@ -871,31 +857,31 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>853.05</v>
+        <v>399.73</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2559.15</v>
+        <v>1598.92</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
     </row>
@@ -907,31 +893,31 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>巧克力礼盒</t>
+          <t>羽毛球拍</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1619.76</v>
+        <v>1743.74</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1619.76</v>
+        <v>1743.74</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
     </row>
@@ -943,7 +929,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>坚果礼盒</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -952,22 +938,22 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1511.06</v>
+        <v>2569.29</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7555.3</v>
+        <v>2569.29</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
     </row>
@@ -979,7 +965,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>坚果礼盒</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -988,22 +974,22 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>779.91</v>
+        <v>1128.44</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>779.91</v>
+        <v>2256.88</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
     </row>
@@ -1015,31 +1001,31 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>帐篷双人</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>874.13</v>
+        <v>1615.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3496.52</v>
+        <v>3230.8</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1037,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>橄榄油</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1060,22 +1046,22 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>252.53</v>
+        <v>681.26</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>505.06</v>
+        <v>2043.78</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
     </row>
@@ -1087,31 +1073,31 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>帐篷双人</t>
+          <t>进口红酒</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1455.66</v>
+        <v>824.1900000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5822.64</v>
+        <v>1648.38</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
     </row>
@@ -1123,31 +1109,31 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>进口红酒</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1576.05</v>
+        <v>453.33</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6304.2</v>
+        <v>906.66</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
     </row>
@@ -1159,26 +1145,26 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>显示器27寸</t>
+          <t>自行车头盔</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1856.21</v>
+        <v>2695.53</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3712.42</v>
+        <v>10782.12</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1195,31 +1181,31 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2424.84</v>
+        <v>299</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9699.360000000001</v>
+        <v>299</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
     </row>
@@ -1231,26 +1217,26 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>毛巾浴巾</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1044.78</v>
+        <v>217.68</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3134.34</v>
+        <v>870.72</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1267,7 +1253,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>自行车头盔</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1276,22 +1262,22 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>965.27</v>
+        <v>2049.44</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2895.81</v>
+        <v>2049.44</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
     </row>
@@ -1303,26 +1289,26 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>906.77</v>
+        <v>1320.25</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4533.85</v>
+        <v>5281</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1339,31 +1325,31 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>巧克力礼盒</t>
+          <t>帐篷双人</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2661.62</v>
+        <v>1536.81</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>13308.1</v>
+        <v>1536.81</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
     </row>
@@ -1375,31 +1361,31 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>卫衣连帽</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2191.76</v>
+        <v>2293.66</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2191.76</v>
+        <v>11468.3</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
     </row>
@@ -1411,31 +1397,31 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1508.05</v>
+        <v>361.25</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4524.15</v>
+        <v>1083.75</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
     </row>
@@ -1447,31 +1433,31 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>羽毛球拍</t>
+          <t>运动短裤</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1166.28</v>
+        <v>2841.44</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5831.4</v>
+        <v>2841.44</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1469,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>望远镜</t>
+          <t>帐篷双人</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1492,22 +1478,22 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>541.51</v>
+        <v>410.32</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1083.02</v>
+        <v>1641.28</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -1519,31 +1505,31 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>围巾羊绒</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1412.27</v>
+        <v>2272.14</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5649.08</v>
+        <v>4544.28</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
     </row>
@@ -1555,26 +1541,26 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>594.7</v>
+        <v>1369.91</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2973.5</v>
+        <v>2739.82</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1591,31 +1577,31 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>羽毛球拍</t>
+          <t>移动硬盘2T</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2993.66</v>
+        <v>1674.15</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>11974.64</v>
+        <v>8370.75</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
     </row>
@@ -1627,26 +1613,26 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>即食燕窝</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>287.73</v>
+        <v>229.18</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1150.92</v>
+        <v>229.18</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1663,7 +1649,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1672,22 +1658,22 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>510.85</v>
+        <v>665.28</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>510.85</v>
+        <v>1330.56</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
     </row>
@@ -1699,31 +1685,31 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1403.78</v>
+        <v>309.15</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5615.12</v>
+        <v>1236.6</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -1735,31 +1721,31 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>进口红酒</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1768.79</v>
+        <v>2028.89</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7075.16</v>
+        <v>2028.89</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1757,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>iPhone 15</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1780,22 +1766,22 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1051.1</v>
+        <v>598.02</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5255.5</v>
+        <v>2990.1</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -1807,31 +1793,31 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>976.46</v>
+        <v>1403.01</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>976.46</v>
+        <v>1403.01</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
     </row>
@@ -1843,31 +1829,31 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>T恤纯棉</t>
+          <t>显示器27寸</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2148.12</v>
+        <v>2512</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2148.12</v>
+        <v>2512</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -1879,31 +1865,31 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1246.41</v>
+        <v>663.83</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2492.82</v>
+        <v>2655.32</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -1915,31 +1901,31 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>运动短裤</t>
+          <t>机械键盘</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1056.64</v>
+        <v>816.65</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5283.2</v>
+        <v>3266.6</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
     </row>
@@ -1951,31 +1937,31 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>T恤纯棉</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>2882.63</v>
+        <v>910.22</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>8647.889999999999</v>
+        <v>910.22</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1973,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>机械键盘</t>
+          <t>iPhone 15</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1996,22 +1982,22 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>2314.74</v>
+        <v>1764.01</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>9258.959999999999</v>
+        <v>8820.049999999999</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
     </row>
@@ -2023,31 +2009,31 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘2T</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1974.5</v>
+        <v>1796.25</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1974.5</v>
+        <v>3592.5</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
     </row>
@@ -2059,31 +2045,31 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>望远镜</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>2394.46</v>
+        <v>147.03</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>7183.38</v>
+        <v>147.03</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
     </row>
@@ -2095,31 +2081,31 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1269.27</v>
+        <v>2018.09</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5077.08</v>
+        <v>6054.27</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -2131,31 +2117,31 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>自行车头盔</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>2628.91</v>
+        <v>1386.96</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>13144.55</v>
+        <v>1386.96</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>上海</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2153,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>显示器27寸</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2176,22 +2162,22 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>849.66</v>
+        <v>662.0700000000001</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1699.32</v>
+        <v>1986.21</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
     </row>
@@ -2203,31 +2189,31 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>卫衣连帽</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>2017.91</v>
+        <v>875.41</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>8071.64</v>
+        <v>3501.64</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
     </row>
@@ -2239,26 +2225,26 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>2475.92</v>
+        <v>2796.32</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4951.84</v>
+        <v>2796.32</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2275,31 +2261,31 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>进口红酒</t>
+          <t>显示器27寸</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>2498.57</v>
+        <v>490.68</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>12492.85</v>
+        <v>1472.04</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
     </row>
@@ -2311,31 +2297,31 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>巧克力礼盒</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>2339.04</v>
+        <v>1530.06</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>11695.2</v>
+        <v>4590.18</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
     </row>
@@ -2347,31 +2333,31 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>有机牛奶</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1252.31</v>
+        <v>39.53</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>5009.24</v>
+        <v>79.06</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南京</t>
         </is>
       </c>
     </row>
@@ -2383,31 +2369,31 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>扫地机器人</t>
+          <t>自行车头盔</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>2145.75</v>
+        <v>1694.89</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>8583</v>
+        <v>1694.89</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
     </row>
@@ -2419,26 +2405,26 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>卫衣连帽</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>936.78</v>
+        <v>2507.75</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>936.78</v>
+        <v>12538.75</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">

--- a/practice-files/day03-筛选与排序.xlsx
+++ b/practice-files/day03-筛选与排序.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,22 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -86,16 +102,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -564,6 +585,41 @@
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>试试筛选+排序的组合：先筛出"上海"的订单，再按金额降序排</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>思考题1: 筛选和排序的本质区别？发报告给同事前应该用哪个？</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" hidden="1" outlineLevel="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 筛选只是"隐藏"不符合条件的行，数据还在原位；排序是真正"重新排列"行的顺序。发报告前先排好序再发，别人打开一眼能看懂。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: 多条件排序"先按位数升序、再按价格降序"是怎么排的？</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" hidden="1" outlineLevel="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 先按位数分组排，位数相同的行内部再按价格从大到小排。是"先主后次"的关系，不是两个条件混成一次排序。</t>
         </is>
       </c>
     </row>
@@ -592,1842 +648,1842 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>价格</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>城市</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ORD-0001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>iPhone 15</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="7" t="n">
         <v>2231.4</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="7" t="n">
         <v>4462.8</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ORD-0002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>登山包</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="7" t="n">
         <v>1782.76</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="7" t="n">
         <v>1782.76</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>2026-01-03</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ORD-0003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>围巾羊绒</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="7" t="n">
         <v>1817</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="7" t="n">
         <v>9085</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>ORD-0004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>棒球帽</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7" t="n">
         <v>1779.12</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="7" t="n">
         <v>1779.12</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>ORD-0005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>巧克力礼盒</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="7" t="n">
         <v>490.77</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="7" t="n">
         <v>1472.31</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>ORD-0006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>小米14</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>2546.06</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="7" t="n">
         <v>12730.3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>ORD-0007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>地毯</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>399.73</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="7" t="n">
         <v>1598.92</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>ORD-0008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>羽毛球拍</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>1743.74</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="7" t="n">
         <v>1743.74</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>ORD-0009</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>坚果礼盒</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>2569.29</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="7" t="n">
         <v>2569.29</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>ORD-0010</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>绿茶龙井</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>1128.44</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="7" t="n">
         <v>2256.88</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>ORD-0011</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>帐篷双人</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="7" t="n">
         <v>1615.4</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="7" t="n">
         <v>3230.8</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>ORD-0012</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>橄榄油</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="7" t="n">
         <v>681.26</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="7" t="n">
         <v>2043.78</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>2026-01-08</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>ORD-0013</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>进口红酒</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="7" t="n">
         <v>824.1900000000001</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="7" t="n">
         <v>1648.38</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>ORD-0014</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>加湿器</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="7" t="n">
         <v>453.33</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="7" t="n">
         <v>906.66</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>ORD-0015</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>自行车头盔</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="7" t="n">
         <v>2695.53</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="7" t="n">
         <v>10782.12</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>ORD-0016</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>滑雪手套</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="7" t="n">
         <v>299</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="7" t="n">
         <v>299</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>ORD-0017</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>毛巾浴巾</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="7" t="n">
         <v>217.68</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="7" t="n">
         <v>870.72</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>ORD-0018</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>瑜伽垫</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="7" t="n">
         <v>2049.44</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="7" t="n">
         <v>2049.44</v>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>ORD-0019</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>华为Mate 60</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="7" t="n">
         <v>1320.25</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="7" t="n">
         <v>5281</v>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>ORD-0020</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>帐篷双人</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="7" t="n">
         <v>1536.81</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="7" t="n">
         <v>1536.81</v>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>ORD-0021</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>卫衣连帽</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="7" t="n">
         <v>2293.66</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="7" t="n">
         <v>11468.3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>ORD-0022</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>乳胶枕头</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="7" t="n">
         <v>361.25</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="7" t="n">
         <v>1083.75</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>ORD-0023</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>运动短裤</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="7" t="n">
         <v>2841.44</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="7" t="n">
         <v>2841.44</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>ORD-0024</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>帐篷双人</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="7" t="n">
         <v>410.32</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="7" t="n">
         <v>1641.28</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>ORD-0025</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>围巾羊绒</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="7" t="n">
         <v>2272.14</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="7" t="n">
         <v>4544.28</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>ORD-0026</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>地毯</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="7" t="n">
         <v>1369.91</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="7" t="n">
         <v>2739.82</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>ORD-0027</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>移动硬盘2T</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="7" t="n">
         <v>1674.15</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="7" t="n">
         <v>8370.75</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>ORD-0028</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>MacBook Pro</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="7" t="n">
         <v>229.18</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="7" t="n">
         <v>229.18</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>ORD-0029</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>蛋白粉</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="7" t="n">
         <v>665.28</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="7" t="n">
         <v>1330.56</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>ORD-0030</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>台灯LED</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="7" t="n">
         <v>309.15</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="7" t="n">
         <v>1236.6</v>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>ORD-0031</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>乳胶枕头</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="7" t="n">
         <v>2028.89</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="7" t="n">
         <v>2028.89</v>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>2026-01-13</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>ORD-0032</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>MacBook Pro</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="7" t="n">
         <v>598.02</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="7" t="n">
         <v>2990.1</v>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>ORD-0033</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>冲锋衣</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="7" t="n">
         <v>1403.01</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="7" t="n">
         <v>1403.01</v>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>ORD-0034</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>显示器27寸</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="7" t="n">
         <v>2512</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="7" t="n">
         <v>2512</v>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>ORD-0035</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>加湿器</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="7" t="n">
         <v>663.83</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="7" t="n">
         <v>2655.32</v>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>2026-01-06</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>ORD-0036</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>机械键盘</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="7" t="n">
         <v>816.65</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="7" t="n">
         <v>3266.6</v>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>ORD-0037</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>T恤纯棉</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="7" t="n">
         <v>910.22</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="7" t="n">
         <v>910.22</v>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>ORD-0038</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>iPhone 15</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="7" t="n">
         <v>1764.01</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="7" t="n">
         <v>8820.049999999999</v>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>ORD-0039</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>羽绒服</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="7" t="n">
         <v>1796.25</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="7" t="n">
         <v>3592.5</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>ORD-0040</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>望远镜</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="7" t="n">
         <v>147.03</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="7" t="n">
         <v>147.03</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>ORD-0041</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>咖啡豆</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="7" t="n">
         <v>2018.09</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="7" t="n">
         <v>6054.27</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>ORD-0042</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>冲锋衣</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="7" t="n">
         <v>1386.96</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="7" t="n">
         <v>1386.96</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>ORD-0043</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>显示器27寸</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="7" t="n">
         <v>662.0700000000001</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="7" t="n">
         <v>1986.21</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>ORD-0044</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>卫衣连帽</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="7" t="n">
         <v>875.41</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="7" t="n">
         <v>3501.64</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>ORD-0045</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>游泳镜</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="7" t="n">
         <v>2796.32</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="7" t="n">
         <v>2796.32</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>ORD-0046</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>显示器27寸</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="7" t="n">
         <v>490.68</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="7" t="n">
         <v>1472.04</v>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>ORD-0047</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>冲锋衣</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="7" t="n">
         <v>1530.06</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="7" t="n">
         <v>4590.18</v>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>2026-01-03</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>ORD-0048</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>有机牛奶</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="7" t="n">
         <v>39.53</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F49" s="7" t="n">
         <v>79.06</v>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>ORD-0049</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>自行车头盔</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="7" t="n">
         <v>1694.89</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="7" t="n">
         <v>1694.89</v>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>ORD-0050</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>瑜伽垫</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="7" t="n">
         <v>2507.75</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="7" t="n">
         <v>12538.75</v>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>广州</t>
         </is>

--- a/practice-files/day03-筛选与排序.xlsx
+++ b/practice-files/day03-筛选与排序.xlsx
@@ -591,7 +591,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
     <row r="21" hidden="1" outlineLevel="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 筛选只是"隐藏"不符合条件的行，数据还在原位；排序是真正"重新排列"行的顺序。发报告前先排好序再发，别人打开一眼能看懂。</t>
+          <t>答案: 筛选只是"隐藏"不符合条件的行，数据还在原位；排序是真正"重新排列"行的顺序。发报告前先排好序再发，别人打开一眼能看懂。</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
     <row r="24" hidden="1" outlineLevel="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 先按位数分组排，位数相同的行内部再按价格从大到小排。是"先主后次"的关系，不是两个条件混成一次排序。</t>
+          <t>答案: 先按位数分组排，位数相同的行内部再按价格从大到小排。是"先主后次"的关系，不是两个条件混成一次排序。</t>
         </is>
       </c>
     </row>

--- a/practice-files/day03-筛选与排序.xlsx
+++ b/practice-files/day03-筛选与排序.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="靓号数据(备用实战)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -588,36 +589,43 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>【备用实战】没有真实靓号数据时，用"靓号数据(备用实战)"工作表练习（结构与真实数据一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>思考题1: 筛选和排序的本质区别？发报告给同事前应该用哪个？</t>
         </is>
       </c>
     </row>
-    <row r="21" hidden="1" outlineLevel="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22" hidden="1" outlineLevel="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>答案: 筛选只是"隐藏"不符合条件的行，数据还在原位；排序是真正"重新排列"行的顺序。发报告前先排好序再发，别人打开一眼能看懂。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>思考题2: 多条件排序"先按位数升序、再按价格降序"是怎么排的？</t>
         </is>
       </c>
     </row>
-    <row r="24" hidden="1" outlineLevel="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25" hidden="1" outlineLevel="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>答案: 先按位数分组排，位数相同的行内部再按价格从大到小排。是"先主后次"的关系，不是两个条件混成一次排序。</t>
         </is>
@@ -2492,4 +2500,1432 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>号码</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>位数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>规律类型</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>价格(乐元)</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>上架状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>05555</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>171</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>322602</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>166789</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>293</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>362345</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>1429401</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>81693406</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>158844</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>629888</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>95777387</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>177</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>93333</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>17693676</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>32870</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>173</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>889579</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>171</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>77434873</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>8123311</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>63456</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>68893734</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>72980699</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>46537888</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>80531</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>092888</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2991241</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>174</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>31939900</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>6716888</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>8776945</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>446</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>79961234</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>4808313</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>139</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>77014363</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>8553311</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>749888</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>447</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>0824888</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>09477888</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>262</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>67190</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>18699</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>49649909</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>213</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>121234</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>4471888</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>421024</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>166</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>46488888</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>171</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>3990888</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>29671756</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>7465544</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>87603</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>34824771</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>087777</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>豹子</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>388</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>4677378</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>465840</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>78755886</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>360576</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>028951</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>321</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>26217888</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>78091343</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>44455</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>AABB</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>196888</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>227</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>0748217</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>496</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>74367136</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>下架</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>6409888</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>172</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>533942</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>172</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>0952145</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>4247451</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/practice-files/day03-筛选与排序.xlsx
+++ b/practice-files/day03-筛选与排序.xlsx
@@ -2508,7 +2508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2516,12 +2516,13 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>号码</t>
+          <t>靓号ID</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -2531,7 +2532,7 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>规律类型</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
@@ -2541,14 +2542,19 @@
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>上架状态</t>
+          <t>购买方式</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>赠送VIP</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>05555</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
@@ -2564,14 +2570,19 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>322602</t>
+          <t>422602</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
@@ -2587,14 +2598,19 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>166789</t>
+          <t>260733</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
@@ -2602,22 +2618,27 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>293</v>
+        <v>137</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>362345</t>
+          <t>462345</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
@@ -2633,18 +2654,23 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1429401</t>
+          <t>52940</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -2652,64 +2678,79 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>81693406</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>158844</t>
+          <t>69514888</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>629888</t>
+          <t>728800</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -2717,22 +2758,27 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>95777387</t>
+          <t>48725511</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -2740,45 +2786,55 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>93333</t>
+          <t>479888</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>112</v>
+        <v>365</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>17693676</t>
+          <t>11634567</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
@@ -2786,26 +2842,31 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>顺子</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>99579868</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -2813,18 +2874,23 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>173</v>
+        <v>58</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>889579</t>
+          <t>587347</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
@@ -2836,22 +2902,27 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>77434873</t>
+          <t>2223623</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -2859,64 +2930,79 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>8123311</t>
+          <t>76909888</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>66</v>
+        <v>276</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>63456</t>
+          <t>99373467</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>68893734</t>
+          <t>90699016</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
@@ -2928,18 +3014,23 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>72980699</t>
+          <t>85567777</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -2947,45 +3038,55 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>46537888</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>80531</t>
+          <t>47452</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
@@ -2997,45 +3098,55 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>092888</t>
+          <t>59663</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2991241</t>
+          <t>59190</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -3043,64 +3154,79 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>174</v>
+        <v>71</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>31939900</t>
+          <t>7716888</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>6716888</t>
+          <t>55319999</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>8776945</t>
+          <t>4545888</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
@@ -3108,114 +3234,139 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>446</v>
+        <v>141</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>79961234</t>
+          <t>883777</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>4808313</t>
+          <t>678888</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>77014363</t>
+          <t>4515678</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>顺子</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>8553311</t>
+          <t>624444</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>749888</t>
+          <t>810947</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
@@ -3223,72 +3374,87 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>447</v>
+        <v>67</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>0824888</t>
+          <t>77190</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>VIP 1个月</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>09477888</t>
+          <t>79993</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>67190</t>
+          <t>1913341</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -3296,18 +3462,23 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>84477</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
@@ -3315,95 +3486,115 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>49649909</t>
+          <t>930022</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>213</v>
+        <v>148</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>121234</t>
+          <t>56488</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>4471888</t>
+          <t>50139904</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>421024</t>
+          <t>39671756</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -3411,18 +3602,23 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>166</v>
+        <v>83</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>46488888</t>
+          <t>78071111</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
@@ -3430,45 +3626,55 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>3990888</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>29671756</t>
+          <t>44824771</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
@@ -3480,45 +3686,55 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>7465544</t>
+          <t>23171</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>VIP 3个月</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>87603</t>
+          <t>83782639</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
@@ -3526,22 +3742,27 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>34824771</t>
+          <t>9404499</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
@@ -3549,45 +3770,55 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>35</v>
+        <v>337</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>087777</t>
+          <t>98676633</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>AABB</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>388</v>
+        <v>312</v>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>4677378</t>
+          <t>76270289</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -3595,22 +3826,27 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>465840</t>
+          <t>72174</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
@@ -3618,22 +3854,27 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>78755886</t>
+          <t>9657809</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -3641,22 +3882,27 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>360576</t>
+          <t>27240050</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -3664,22 +3910,27 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>028951</t>
+          <t>32219693</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -3687,41 +3938,51 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>26217888</t>
+          <t>1748217</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>152</v>
+        <v>496</v>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>78091343</t>
+          <t>84367136</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
@@ -3733,91 +3994,111 @@
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>竞拍</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>44455</t>
+          <t>19745678</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>AABB</t>
+          <t>顺子</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>196888</t>
+          <t>81111</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>227</v>
+        <v>285</v>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>0748217</t>
+          <t>958888</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>496</v>
+        <v>90</v>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>74367136</t>
+          <t>6171236</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -3825,22 +4106,27 @@
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>146</v>
+        <v>438</v>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>下架</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>6409888</t>
+          <t>91754888</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -3848,22 +4134,27 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>533942</t>
+          <t>4174612</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -3871,22 +4162,27 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>172</v>
+        <v>11</v>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>0952145</t>
+          <t>367586</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
@@ -3894,22 +4190,27 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>直接购买</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>VIP 6个月</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>4247451</t>
+          <t>50537735</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -3917,11 +4218,16 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>未售</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
